--- a/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\MSN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10079B67-3558-4762-AE1B-F0D7FC727299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC304EF5-0DB6-4985-9753-0050D9150C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSN" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="671">
   <si>
     <t>index</t>
   </si>
@@ -2234,9 +2234,6 @@
     <t>PSQI_comp1_subjective_sleepquality</t>
   </si>
   <si>
-    <t>recode(1=0; 2=0; 3=1; 4=1; ELSE=NA)</t>
-  </si>
-  <si>
     <t>The study-specific variable categories 0 = Very good and 1 = Fairly good were coded as DataSchema variable category 0 = Never/Rarely. The study-specific variable categories  2 = Fairly bad and 3 = Very bad were coded as DataSchema variable category 1 = Some difficulties.</t>
   </si>
   <si>
@@ -2290,15 +2287,6 @@
 In a typical week during the past 4 weeks, did you do heavy exercise (such as aerobics, aquajogging, rope skipping, or heavy strenght training)?</t>
   </si>
   <si>
-    <t>Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
-A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
-  </si>
-  <si>
-    <t>case_when(
-activity_Q04_done == 1 | activity_Q09_done ==1 | activity_Q10_done == 1 | activity_Q11_done ==1 | activity_Q12_done ==1 | activity_Q14_done == 1 ~ 1L ; 
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>Based on the variables in the online data dictionary. Are all variables available and part of the input dataset? Confirm if available in follow-up. If so, confirm variable names.</t>
   </si>
   <si>
@@ -2366,6 +2354,45 @@
     <t>case_when(
 !is.na(nit_alcoholtot.ph2) &amp; nit_alcoholtot.ph2 != -888 ~ as.numeric(nit_alcoholtot.ph2)*7 ; 
 ELSE ~ NA_real_)</t>
+  </si>
+  <si>
+    <t>Confirmed same format.</t>
+  </si>
+  <si>
+    <t>Not in follow-up, but could take from baseline. Changed to impossible, add comment.</t>
+  </si>
+  <si>
+    <t>Not available in follow-up, but available in baseline.</t>
+  </si>
+  <si>
+    <t>smoking_unitsperday.ph2 is available but needs to be requested.</t>
+  </si>
+  <si>
+    <t>Available, only at FUP, but need to request.
+recode(1=0; 2=0; 3=1; 4=1; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>Available, but need to request.</t>
+  </si>
+  <si>
+    <t>Available, but need to request.
+case_when(
+activity_Q04_done == 1 | activity_Q09_done ==1 | activity_Q10_done == 1 | activity_Q11_done ==1 | activity_Q12_done ==1 | activity_Q14_done == 1 ~ 1L ; 
+ELSE ~ NA_integer_)
+Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
+A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
+  </si>
+  <si>
+    <t>Available, need to request.</t>
+  </si>
+  <si>
+    <t>Available, but need to request and probably to clean. 
+To request and evaluate, but might not be compatible.</t>
+  </si>
+  <si>
+    <t>Available, but need to request and probably to clean. 
+To request and evaluate, but might not be compatible.
+Will be empty unless said yes to cancer other than skin cancer.</t>
   </si>
 </sst>
 </file>
@@ -2833,7 +2860,8 @@
     <col min="26" max="26" width="50.7109375" style="1" customWidth="1"/>
     <col min="27" max="27" width="61" style="1" customWidth="1"/>
     <col min="28" max="28" width="53" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="28.7109375" style="3"/>
+    <col min="29" max="29" width="43.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="28.7109375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3162,6 +3190,9 @@
       <c r="AA6" s="11" t="s">
         <v>608</v>
       </c>
+      <c r="AC6" s="3" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="7" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -3520,17 +3551,20 @@
       <c r="P14" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="U14" s="3" t="s">
+        <v>663</v>
+      </c>
       <c r="V14" s="5" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="Y14" s="5" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>118</v>
@@ -3540,6 +3574,9 @@
       </c>
       <c r="AB14" s="1" t="s">
         <v>612</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -3954,7 +3991,7 @@
         <v>146</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>174</v>
@@ -3975,7 +4012,7 @@
         <v>175</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4001,7 +4038,7 @@
         <v>152</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>174</v>
@@ -4022,7 +4059,7 @@
         <v>178</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4618,7 +4655,7 @@
         <v>248</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -5016,13 +5053,13 @@
         <v>103</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>289</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5174,7 +5211,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -5213,17 +5250,17 @@
       <c r="P49" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y49" s="8" t="s">
-        <v>89</v>
+      <c r="V49" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W49" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X49" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y49" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z49" s="1" t="s">
         <v>311</v>
@@ -5234,8 +5271,11 @@
       <c r="AB49" s="1" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC49" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -5277,7 +5317,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="135" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -5339,7 +5379,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -5380,31 +5420,34 @@
         <v>626</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="W52" s="5" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="X52" s="5" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="Y52" s="5" t="s">
-        <v>628</v>
+        <v>119</v>
       </c>
       <c r="Z52" s="1" t="s">
         <v>325</v>
       </c>
       <c r="AA52" s="11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+      <c r="AC52" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -5452,7 +5495,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -5497,7 +5540,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -5542,7 +5585,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="315" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="315" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -5587,7 +5630,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -5635,7 +5678,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -5684,7 +5727,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -5733,7 +5776,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -5778,7 +5821,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5807,14 +5850,14 @@
         <v>355</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="O61" s="11"/>
       <c r="P61" s="3" t="s">
         <v>32</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="V61" s="5" t="s">
         <v>119</v>
@@ -5832,13 +5875,16 @@
         <v>356</v>
       </c>
       <c r="AA61" s="11" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+      <c r="AC61" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5883,7 +5929,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="255" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5912,10 +5958,10 @@
         <v>94</v>
       </c>
       <c r="M63" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="N63" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>638</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>522</v>
@@ -5924,34 +5970,35 @@
         <v>32</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>640</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="U63" s="11"/>
       <c r="V63" s="11" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="W63" s="11" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="X63" s="11" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="Y63" s="11" t="s">
-        <v>641</v>
+        <v>119</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>365</v>
       </c>
       <c r="AA63" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AB63" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+      <c r="AC63" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5996,7 +6043,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -6047,7 +6094,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -6098,7 +6145,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -6149,7 +6196,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -6199,7 +6246,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="165" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="165" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -6255,7 +6302,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -6290,26 +6337,29 @@
       <c r="P70" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V70" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W70" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X70" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y70" s="4" t="s">
-        <v>89</v>
+      <c r="V70" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W70" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X70" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y70" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z70" s="1" t="s">
         <v>416</v>
       </c>
       <c r="AA70" s="11" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="AC70" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -6349,26 +6399,29 @@
       <c r="P71" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W71" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y71" s="8" t="s">
-        <v>89</v>
+      <c r="V71" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W71" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X71" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y71" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z71" s="1" t="s">
         <v>423</v>
       </c>
       <c r="AA71" s="11" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="AC71" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -6408,26 +6461,29 @@
       <c r="P72" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y72" s="8" t="s">
-        <v>89</v>
+      <c r="V72" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W72" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X72" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y72" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z72" s="1" t="s">
         <v>430</v>
       </c>
       <c r="AA72" s="11" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -6467,26 +6523,29 @@
       <c r="P73" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V73" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W73" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X73" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y73" s="8" t="s">
-        <v>89</v>
+      <c r="V73" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W73" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X73" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y73" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z73" s="1" t="s">
         <v>436</v>
       </c>
       <c r="AA73" s="11" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="AC73" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6534,7 +6593,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -6582,7 +6641,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -6620,17 +6679,17 @@
       <c r="P76" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y76" s="4" t="s">
-        <v>89</v>
+      <c r="V76" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W76" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X76" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y76" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z76" s="1" t="s">
         <v>451</v>
@@ -6638,8 +6697,11 @@
       <c r="AA76" s="11" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="77" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="AC76" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -6679,17 +6741,17 @@
       <c r="P77" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V77" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W77" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="X77" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y77" s="4" t="s">
-        <v>89</v>
+      <c r="V77" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W77" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X77" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y77" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="Z77" s="1" t="s">
         <v>458</v>
@@ -6697,8 +6759,11 @@
       <c r="AA77" s="11" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="78" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="AC77" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -6743,7 +6808,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -6799,7 +6864,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="90" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -6846,7 +6911,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -6886,17 +6951,17 @@
       <c r="P81" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W81" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="X81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y81" s="8" t="s">
-        <v>89</v>
+      <c r="V81" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W81" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X81" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y81" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="Z81" s="1" t="s">
         <v>485</v>
@@ -6904,8 +6969,11 @@
       <c r="AA81" s="11" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="82" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="AC81" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -6937,29 +7005,32 @@
       <c r="P82" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V82" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W82" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X82" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y82" s="4" t="s">
-        <v>89</v>
+      <c r="V82" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W82" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X82" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y82" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="Z82" s="1" t="s">
         <v>490</v>
       </c>
       <c r="AA82" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AB82" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+      <c r="AC82" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -6991,23 +7062,26 @@
       <c r="P83" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y83" s="4" t="s">
-        <v>89</v>
+      <c r="V83" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W83" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X83" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y83" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA83" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC83" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -7039,23 +7113,26 @@
       <c r="P84" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V84" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W84" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X84" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y84" s="4" t="s">
-        <v>89</v>
+      <c r="V84" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W84" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X84" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y84" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA84" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC84" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -7087,23 +7164,26 @@
       <c r="P85" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W85" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y85" s="4" t="s">
-        <v>89</v>
+      <c r="V85" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W85" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X85" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y85" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA85" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC85" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -7135,23 +7215,26 @@
       <c r="P86" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V86" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W86" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X86" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y86" s="4" t="s">
-        <v>89</v>
+      <c r="V86" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W86" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X86" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y86" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA86" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC86" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -7183,23 +7266,26 @@
       <c r="P87" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V87" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W87" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X87" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y87" s="4" t="s">
-        <v>89</v>
+      <c r="V87" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W87" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X87" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y87" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA87" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC87" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -7231,23 +7317,26 @@
       <c r="P88" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V88" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W88" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X88" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y88" s="4" t="s">
-        <v>89</v>
+      <c r="V88" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W88" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X88" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y88" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA88" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC88" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -7279,23 +7368,26 @@
       <c r="P89" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y89" s="4" t="s">
-        <v>89</v>
+      <c r="V89" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W89" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X89" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y89" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA89" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC89" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -7327,23 +7419,26 @@
       <c r="P90" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V90" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W90" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X90" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y90" s="4" t="s">
-        <v>89</v>
+      <c r="V90" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W90" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X90" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y90" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA90" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC90" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7375,23 +7470,26 @@
       <c r="P91" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y91" s="4" t="s">
-        <v>89</v>
+      <c r="V91" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W91" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X91" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y91" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA91" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC91" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7428,17 +7526,17 @@
       <c r="P92" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V92" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W92" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X92" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y92" s="8" t="s">
-        <v>89</v>
+      <c r="V92" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W92" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X92" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y92" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="Z92" s="1" t="s">
         <v>523</v>
@@ -7446,8 +7544,11 @@
       <c r="AA92" s="11" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="93" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+      <c r="AC92" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7479,23 +7580,26 @@
       <c r="P93" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V93" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W93" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X93" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y93" s="4" t="s">
-        <v>89</v>
+      <c r="V93" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W93" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X93" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y93" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA93" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC93" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -7527,23 +7631,26 @@
       <c r="P94" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y94" s="4" t="s">
-        <v>89</v>
+      <c r="V94" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W94" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X94" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y94" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA94" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC94" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7575,23 +7682,26 @@
       <c r="P95" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V95" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W95" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X95" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y95" s="4" t="s">
-        <v>89</v>
+      <c r="V95" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W95" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X95" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y95" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA95" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC95" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -7623,23 +7733,26 @@
       <c r="P96" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V96" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W96" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X96" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y96" s="4" t="s">
-        <v>89</v>
+      <c r="V96" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W96" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X96" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y96" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA96" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC96" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7671,23 +7784,26 @@
       <c r="P97" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V97" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W97" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X97" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y97" s="4" t="s">
-        <v>89</v>
+      <c r="V97" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W97" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X97" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y97" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA97" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC97" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -7719,23 +7835,26 @@
       <c r="P98" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V98" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W98" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X98" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y98" s="4" t="s">
-        <v>89</v>
+      <c r="V98" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W98" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X98" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y98" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA98" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC98" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7767,23 +7886,26 @@
       <c r="P99" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V99" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W99" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X99" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y99" s="4" t="s">
-        <v>89</v>
+      <c r="V99" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W99" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X99" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y99" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA99" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC99" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7815,23 +7937,26 @@
       <c r="P100" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y100" s="4" t="s">
-        <v>89</v>
+      <c r="V100" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="W100" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="X100" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y100" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="AA100" s="11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="AC100" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7876,7 +8001,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -7905,14 +8030,14 @@
         <v>41</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="O102" s="9"/>
       <c r="P102" s="3" t="s">
         <v>32</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="V102" s="5" t="s">
         <v>89</v>
@@ -7930,10 +8055,10 @@
         <v>556</v>
       </c>
       <c r="AB102" s="11" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -7978,7 +8103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -8031,7 +8156,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -8084,7 +8209,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -8134,7 +8259,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -8176,7 +8301,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -8218,7 +8343,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8260,7 +8385,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8303,7 +8428,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8353,7 +8478,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8447,13 +8572,13 @@
         <v>24</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>51</v>
@@ -8477,7 +8602,7 @@
         <v>89</v>
       </c>
       <c r="AB114" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
@@ -8488,13 +8613,13 @@
         <v>24</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>51</v>
@@ -8518,7 +8643,7 @@
         <v>89</v>
       </c>
       <c r="AB115" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
@@ -8529,13 +8654,13 @@
         <v>24</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>51</v>
@@ -8559,7 +8684,7 @@
         <v>89</v>
       </c>
       <c r="AB116" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
@@ -8570,13 +8695,13 @@
         <v>24</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>51</v>
@@ -8600,7 +8725,7 @@
         <v>89</v>
       </c>
       <c r="AB117" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC304EF5-0DB6-4985-9753-0050D9150C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3D4467-982A-46C6-99D5-7EC253F68CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="661">
   <si>
     <t>index</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>Must be unique within the study.</t>
-  </si>
-  <si>
-    <t>Deelnemer_ID</t>
   </si>
   <si>
     <t>unique particiapnt ID</t>
@@ -2309,36 +2306,6 @@
     <t>From MINI depression</t>
   </si>
   <si>
-    <t>dth_status</t>
-  </si>
-  <si>
-    <t>dth_date_day</t>
-  </si>
-  <si>
-    <t>dth_date_month</t>
-  </si>
-  <si>
-    <t>dth_date_year</t>
-  </si>
-  <si>
-    <t>Death status</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is deceased</t>
-  </si>
-  <si>
-    <t>Death date - Day</t>
-  </si>
-  <si>
-    <t>Death date - Month</t>
-  </si>
-  <si>
-    <t>Death date - Year</t>
-  </si>
-  <si>
-    <t>Information about death in linkage dataset.</t>
-  </si>
-  <si>
     <t>waist.ph2</t>
   </si>
   <si>
@@ -2393,6 +2360,9 @@
     <t>Available, but need to request and probably to clean. 
 To request and evaluate, but might not be compatible.
 Will be empty unless said yes to cancer other than skin cancer.</t>
+  </si>
+  <si>
+    <t>Deelnemer_ID</t>
   </si>
 </sst>
 </file>
@@ -2837,7 +2807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF117"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="3" customWidth="1"/>
@@ -2926,7 +2896,7 @@
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>20</v>
@@ -2941,25 +2911,25 @@
         <v>23</v>
       </c>
       <c r="Z1" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -2985,28 +2955,28 @@
         <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="P2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -3017,37 +2987,37 @@
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3" s="3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -3058,37 +3028,37 @@
         <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X4" s="3" t="s">
+      <c r="Y4" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -3099,34 +3069,34 @@
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="Y5" s="4">
         <v>2</v>
@@ -3140,58 +3110,58 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W6" s="3" t="s">
+      <c r="X6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="Y6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Z6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Z6" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AA6" s="11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="30" x14ac:dyDescent="0.25">
@@ -3202,43 +3172,43 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X7" s="3" t="s">
+      <c r="Y7" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -3249,49 +3219,49 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="Y8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
@@ -3302,40 +3272,40 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="30" x14ac:dyDescent="0.25">
@@ -3346,40 +3316,40 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="M10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="90" x14ac:dyDescent="0.25">
@@ -3390,46 +3360,46 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="O11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X11" s="3" t="s">
+      <c r="Y11" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="30" x14ac:dyDescent="0.25">
@@ -3440,43 +3410,43 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -3487,37 +3457,37 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W13" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="120" x14ac:dyDescent="0.25">
@@ -3528,55 +3498,55 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="M14" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="P14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="W14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB14" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="W14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="X14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA14" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="AC14" s="3" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -3587,46 +3557,46 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="L15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y15" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y15" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="135" x14ac:dyDescent="0.25">
@@ -3637,43 +3607,43 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="O16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="P16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y16" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y16" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
@@ -3684,43 +3654,43 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="M17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3731,46 +3701,46 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="P18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y18" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3781,40 +3751,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y19" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3825,46 +3795,46 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="P20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y20" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y20" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3875,40 +3845,40 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y21" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3919,47 +3889,47 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="J22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="P22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y22" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -3970,49 +3940,49 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="N23" s="3" t="s">
+      <c r="P23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y23" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y23" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="AB23" s="1" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4023,43 +3993,43 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y24" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="AB24" s="1" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4070,40 +4040,40 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="M25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z25" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W25" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4114,37 +4084,37 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4155,46 +4125,46 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="P27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y27" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y27" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4205,46 +4175,46 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="P28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y28" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y28" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4255,46 +4225,46 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="J29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="M29" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="P29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y29" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y29" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4305,46 +4275,46 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="K30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K30" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="M30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W30" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
@@ -4355,37 +4325,37 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="M31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X31" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
@@ -4396,38 +4366,38 @@
         <v>24</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W32" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X32" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4438,40 +4408,40 @@
         <v>24</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="M33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="N33" s="3" t="s">
+      <c r="P33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y33" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y33" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4482,41 +4452,41 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="N34" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="N34" s="7" t="s">
+      <c r="P34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y34" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y34" s="4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4527,40 +4497,40 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="M35" s="1" t="s">
+      <c r="N35" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="P35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y35" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y35" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4571,40 +4541,40 @@
         <v>24</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="P36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y36" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y36" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -4615,47 +4585,47 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="P37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y37" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="P37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y37" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="AB37" s="1" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4666,41 +4636,41 @@
         <v>24</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="N38" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="P38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y38" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V38" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W38" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X38" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y38" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4711,41 +4681,41 @@
         <v>24</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W39" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W39" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X39" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y39" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4756,48 +4726,48 @@
         <v>24</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="M40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="9"/>
       <c r="P40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W40" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W40" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y40" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4808,44 +4778,44 @@
         <v>24</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O41" s="9"/>
       <c r="P41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X41" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y41" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4856,48 +4826,48 @@
         <v>24</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="J42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X42" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -4908,47 +4878,47 @@
         <v>24</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="L43" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W43" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X43" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -4959,47 +4929,47 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="O44" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O44" s="9" t="s">
+      <c r="P44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y44" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y44" s="4" t="s">
+      <c r="Z44" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5010,56 +4980,56 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="N45" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="O45" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y45" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="Z45" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y45" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="Z45" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="AB45" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5070,41 +5040,41 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="M46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9"/>
       <c r="P46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X46" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y46" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="135" x14ac:dyDescent="0.25">
@@ -5115,49 +5085,49 @@
         <v>24</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="O47" s="1" t="s">
+      <c r="P47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y47" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y47" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5168,47 +5138,47 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="M48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O48" s="9"/>
       <c r="P48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W48" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X48" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y48" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5219,60 +5189,60 @@
         <v>24</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="K49" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O49" s="9"/>
       <c r="P49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z49" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AA49" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="AB49" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AB49" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="AC49" s="3" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
@@ -5283,38 +5253,38 @@
         <v>24</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F50" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="M50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O50" s="9"/>
       <c r="P50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W50" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W50" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X50" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y50" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:29" ht="135" x14ac:dyDescent="0.25">
@@ -5325,58 +5295,58 @@
         <v>24</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J51" s="3" t="s">
+      <c r="L51" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="M51" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="N51" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="U51" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="V51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="W51" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="X51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z51" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="N51" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="V51" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="W51" s="5" t="s">
+      <c r="AB51" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="X51" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y51" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z51" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB51" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -5387,64 +5357,64 @@
         <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="V52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z52" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="U52" s="3" t="s">
+      <c r="AA52" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="AB52" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="V52" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W52" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X52" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y52" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z52" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="AA52" s="11" t="s">
-        <v>630</v>
-      </c>
-      <c r="AB52" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="AC52" s="1" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
     </row>
     <row r="53" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5455,44 +5425,44 @@
         <v>24</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J53" s="3" t="s">
+      <c r="L53" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="M53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V53" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W53" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X53" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y53" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5503,41 +5473,41 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O54" s="9"/>
       <c r="P54" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V54" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W54" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X54" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y54" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z54" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5548,41 +5518,41 @@
         <v>24</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O55" s="9"/>
       <c r="P55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V55" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W55" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W55" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X55" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y55" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:29" ht="315" x14ac:dyDescent="0.25">
@@ -5593,41 +5563,41 @@
         <v>24</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="M56" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O56" s="9"/>
       <c r="P56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V56" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W56" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W56" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X56" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y56" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5638,44 +5608,44 @@
         <v>24</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="F57" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="M57" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O57" s="9"/>
       <c r="P57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V57" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W57" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X57" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y57" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z57" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5686,45 +5656,45 @@
         <v>24</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>343</v>
-      </c>
       <c r="F58" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J58" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="M58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="9"/>
       <c r="P58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V58" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W58" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X58" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y58" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z58" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5735,45 +5705,45 @@
         <v>24</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F59" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O59" s="9"/>
       <c r="P59" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X59" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y59" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:29" ht="135" x14ac:dyDescent="0.25">
@@ -5784,41 +5754,41 @@
         <v>24</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="M60" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O60" s="9"/>
       <c r="P60" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V60" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W60" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X60" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y60" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -5829,59 +5799,59 @@
         <v>24</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K61" s="3" t="s">
+      <c r="L61" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="M61" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="M61" s="11" t="s">
-        <v>355</v>
-      </c>
       <c r="N61" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="O61" s="11"/>
       <c r="P61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T61" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="V61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z61" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AA61" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="AB61" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="V61" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W61" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X61" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y61" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z61" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA61" s="11" t="s">
-        <v>635</v>
-      </c>
-      <c r="AB61" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="AC61" s="3" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="62" spans="1:29" ht="105" x14ac:dyDescent="0.25">
@@ -5892,41 +5862,41 @@
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="M62" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O62" s="9"/>
       <c r="P62" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W62" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X62" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y62" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -5937,65 +5907,65 @@
         <v>24</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="K63" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M63" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="N63" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="N63" s="1" t="s">
+      <c r="O63" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T63" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="U63" s="11"/>
       <c r="V63" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W63" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X63" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y63" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z63" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA63" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AB63" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AC63" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="64" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -6006,41 +5976,41 @@
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="F64" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="L64" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O64" s="9"/>
       <c r="P64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V64" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W64" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W64" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X64" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y64" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -6051,47 +6021,47 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J65" s="3" t="s">
+      <c r="K65" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M65" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="K65" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M65" s="1" t="s">
+      <c r="N65" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V65" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V65" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="W65" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y65" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
@@ -6102,47 +6072,47 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="N66" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="N66" s="1" t="s">
+      <c r="O66" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="O66" s="1" t="s">
+      <c r="P66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y66" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y66" s="4" t="s">
+      <c r="Z66" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="Z66" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
@@ -6153,47 +6123,47 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="N67" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="O67" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="O67" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="P67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V67" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V67" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="W67" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X67" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="X67" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="Y67" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z67" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="Z67" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6204,46 +6174,46 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K68" s="3" t="s">
+      <c r="L68" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="N68" s="3" t="s">
+      <c r="O68" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="O68" s="1" t="s">
+      <c r="P68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W68" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X68" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y68" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V68" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W68" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X68" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y68" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="165" x14ac:dyDescent="0.25">
@@ -6254,52 +6224,52 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J69" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J69" s="3" t="s">
+      <c r="K69" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="L69" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="M69" s="8" t="s">
+      <c r="N69" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="O69" s="1" t="s">
+      <c r="P69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="X69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y69" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="Z69" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="W69" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y69" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="Z69" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6310,53 +6280,53 @@
         <v>24</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="F70" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="L70" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O70" s="9"/>
       <c r="P70" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V70" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W70" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X70" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y70" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z70" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AA70" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AC70" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6367,58 +6337,58 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="J71" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N71" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M71" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N71" s="3" t="s">
+      <c r="O71" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="O71" s="9" t="s">
+      <c r="P71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z71" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="P71" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V71" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W71" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X71" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y71" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z71" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="AA71" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AC71" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6429,58 +6399,58 @@
         <v>24</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="J72" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M72" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N72" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M72" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N72" s="1" t="s">
+      <c r="O72" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="O72" s="9" t="s">
+      <c r="P72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z72" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V72" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W72" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X72" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y72" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z72" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="AA72" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AC72" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6491,58 +6461,58 @@
         <v>24</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="F73" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I73" s="3" t="s">
+      <c r="J73" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M73" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N73" s="3" t="s">
+      <c r="O73" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z73" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="O73" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z73" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="AA73" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AC73" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -6553,44 +6523,44 @@
         <v>24</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="F74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="J74" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O74" s="9"/>
       <c r="P74" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V74" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W74" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W74" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X74" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y74" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -6601,44 +6571,44 @@
         <v>24</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="F75" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O75" s="9"/>
       <c r="P75" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V75" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W75" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W75" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X75" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y75" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -6649,56 +6619,56 @@
         <v>24</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="F76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="J76" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="K76" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O76" s="9"/>
       <c r="P76" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V76" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W76" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X76" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y76" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z76" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AA76" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AC76" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -6709,58 +6679,58 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="F77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="J77" s="3" t="s">
+      <c r="L77" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N77" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M77" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="O77" s="1" t="s">
+      <c r="P77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z77" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="P77" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V77" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W77" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X77" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y77" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z77" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="AA77" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AC77" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -6771,41 +6741,41 @@
         <v>24</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="L78" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O78" s="9"/>
       <c r="P78" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V78" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W78" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W78" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X78" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y78" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6816,52 +6786,52 @@
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="F79" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="J79" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="K79" s="3" t="s">
+      <c r="L79" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M79" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="L79" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="N79" s="3" t="s">
+      <c r="O79" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="O79" s="1" t="s">
+      <c r="P79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W79" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X79" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y79" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V79" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W79" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X79" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y79" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -6872,43 +6842,43 @@
         <v>24</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="O80" s="1" t="s">
+      <c r="P80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V80" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W80" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X80" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y80" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V80" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W80" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X80" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y80" s="4" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -6919,58 +6889,58 @@
         <v>24</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N81" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="L81" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M81" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N81" s="1" t="s">
+      <c r="O81" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="O81" s="9" t="s">
+      <c r="P81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="W81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z81" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V81" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="W81" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="X81" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y81" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z81" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="AA81" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AC81" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -6981,53 +6951,53 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="F82" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="L82" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O82" s="9"/>
       <c r="P82" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V82" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W82" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X82" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y82" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z82" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AA82" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="AB82" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="AB82" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="AC82" s="1" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="83" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7038,47 +7008,47 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="F83" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O83" s="9"/>
       <c r="P83" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V83" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W83" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X83" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y83" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA83" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC83" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7089,47 +7059,47 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="F84" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O84" s="9"/>
       <c r="P84" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V84" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W84" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X84" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y84" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA84" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC84" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="85" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7140,47 +7110,47 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>499</v>
-      </c>
       <c r="F85" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O85" s="9"/>
       <c r="P85" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA85" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC85" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="86" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7191,47 +7161,47 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="F86" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O86" s="9"/>
       <c r="P86" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V86" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W86" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X86" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y86" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA86" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC86" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7242,47 +7212,47 @@
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>505</v>
-      </c>
       <c r="F87" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O87" s="9"/>
       <c r="P87" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V87" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W87" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X87" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y87" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA87" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC87" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7293,47 +7263,47 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="F88" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O88" s="9"/>
       <c r="P88" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V88" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W88" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X88" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y88" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA88" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC88" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="89" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7344,47 +7314,47 @@
         <v>24</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>511</v>
-      </c>
       <c r="F89" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O89" s="9"/>
       <c r="P89" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V89" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W89" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X89" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y89" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA89" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC89" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="90" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7395,47 +7365,47 @@
         <v>24</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="F90" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O90" s="9"/>
       <c r="P90" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V90" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W90" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X90" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y90" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA90" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC90" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7446,47 +7416,47 @@
         <v>24</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>517</v>
-      </c>
       <c r="F91" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O91" s="9"/>
       <c r="P91" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V91" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W91" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X91" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y91" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA91" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC91" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -7497,55 +7467,55 @@
         <v>24</v>
       </c>
       <c r="C92" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="F92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N92" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N92" s="1" t="s">
+      <c r="O92" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="O92" s="9" t="s">
+      <c r="P92" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="W92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z92" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="P92" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V92" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="W92" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="X92" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y92" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z92" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="AA92" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AC92" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="93" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7556,47 +7526,47 @@
         <v>24</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>526</v>
-      </c>
       <c r="F93" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O93" s="9"/>
       <c r="P93" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V93" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W93" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X93" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y93" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA93" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC93" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="94" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7607,47 +7577,47 @@
         <v>24</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="E94" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>529</v>
-      </c>
       <c r="F94" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O94" s="9"/>
       <c r="P94" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V94" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W94" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X94" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y94" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA94" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC94" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7658,47 +7628,47 @@
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="E95" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>532</v>
-      </c>
       <c r="F95" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O95" s="9"/>
       <c r="P95" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V95" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W95" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X95" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y95" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA95" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC95" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="96" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7709,47 +7679,47 @@
         <v>24</v>
       </c>
       <c r="C96" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>535</v>
-      </c>
       <c r="F96" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O96" s="9"/>
       <c r="P96" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V96" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W96" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X96" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y96" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA96" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC96" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="97" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7760,47 +7730,47 @@
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="F97" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O97" s="9"/>
       <c r="P97" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V97" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W97" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X97" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y97" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA97" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC97" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="98" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7811,47 +7781,47 @@
         <v>24</v>
       </c>
       <c r="C98" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>541</v>
-      </c>
       <c r="F98" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O98" s="9"/>
       <c r="P98" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V98" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W98" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X98" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y98" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA98" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC98" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="99" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7862,47 +7832,47 @@
         <v>24</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="F99" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O99" s="9"/>
       <c r="P99" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V99" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W99" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X99" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y99" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA99" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC99" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7913,47 +7883,47 @@
         <v>24</v>
       </c>
       <c r="C100" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>547</v>
-      </c>
       <c r="F100" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O100" s="9"/>
       <c r="P100" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V100" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W100" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X100" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y100" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA100" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC100" s="1" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.25">
@@ -7964,41 +7934,41 @@
         <v>24</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="E101" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J101" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>551</v>
-      </c>
       <c r="L101" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O101" s="9"/>
       <c r="P101" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V101" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W101" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X101" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y101" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -8009,53 +7979,53 @@
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="F102" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J102" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>555</v>
-      </c>
       <c r="L102" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M102" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="O102" s="9"/>
       <c r="P102" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="V102" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W102" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="X102" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y102" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AB102" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.25">
@@ -8066,41 +8036,41 @@
         <v>24</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>559</v>
-      </c>
       <c r="F103" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O103" s="9"/>
       <c r="P103" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V103" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W103" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W103" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X103" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y103" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8111,49 +8081,49 @@
         <v>24</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="E104" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J104" s="3" t="s">
+      <c r="L104" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M104" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="M104" s="1" t="s">
+      <c r="N104" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="N104" s="3" t="s">
+      <c r="O104" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="O104" s="1" t="s">
+      <c r="P104" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V104" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X104" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y104" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z104" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="P104" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V104" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W104" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X104" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y104" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z104" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="105" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -8164,49 +8134,49 @@
         <v>24</v>
       </c>
       <c r="C105" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="E105" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J105" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E105" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J105" s="3" t="s">
+      <c r="L105" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M105" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="L105" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="M105" s="1" t="s">
+      <c r="N105" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="N105" s="3" t="s">
+      <c r="O105" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="P105" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V105" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X105" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y105" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z105" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="P105" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V105" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W105" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X105" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y105" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z105" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -8217,46 +8187,46 @@
         <v>24</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="E106" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M106" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="M106" s="1" t="s">
+      <c r="N106" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="N106" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="O106" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P106" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V106" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V106" s="3" t="s">
+      <c r="W106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="W106" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X106" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y106" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.25">
@@ -8267,38 +8237,38 @@
         <v>24</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="E107" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J107" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>579</v>
-      </c>
       <c r="M107" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O107" s="9"/>
       <c r="P107" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V107" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W107" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W107" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X107" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y107" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.25">
@@ -8309,38 +8279,38 @@
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="E108" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J108" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="M108" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O108" s="9"/>
       <c r="P108" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V108" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W108" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W108" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X108" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y108" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.25">
@@ -8351,38 +8321,38 @@
         <v>24</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="E109" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J109" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="M109" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O109" s="9"/>
       <c r="P109" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V109" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W109" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W109" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X109" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y109" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.25">
@@ -8393,39 +8363,39 @@
         <v>24</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="E110" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J110" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O110" s="9"/>
       <c r="P110" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V110" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W110" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W110" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X110" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y110" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
@@ -8436,46 +8406,46 @@
         <v>24</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="E111" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J111" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J111" s="3" t="s">
+      <c r="M111" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="M111" s="1" t="s">
+      <c r="N111" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="N111" s="1" t="s">
+      <c r="O111" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="O111" s="1" t="s">
+      <c r="P111" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V111" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W111" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="X111" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y111" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="P111" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V111" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W111" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X111" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y111" s="10" t="s">
+      <c r="Z111" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="Z111" s="1" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.25">
@@ -8486,42 +8456,42 @@
         <v>24</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>598</v>
-      </c>
       <c r="E112" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L112" s="1"/>
       <c r="M112" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O112" s="9"/>
       <c r="P112" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V112" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W112" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W112" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X112" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y112" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -8529,203 +8499,39 @@
         <v>24</v>
       </c>
       <c r="C113" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>600</v>
-      </c>
       <c r="E113" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O113" s="9"/>
       <c r="P113" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V113" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W113" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W113" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="X113" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y113" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P114" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V114" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W114" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X114" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y114" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB114" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P115" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V115" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W115" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X115" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y115" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB115" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P116" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V116" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W116" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X116" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y116" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB116" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M117" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P117" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V117" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W117" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="X117" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y117" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB117" s="1" t="s">
-        <v>655</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3D4467-982A-46C6-99D5-7EC253F68CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7595E99-404F-4084-8244-57049F550AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="658">
   <si>
     <t>index</t>
   </si>
@@ -1226,10 +1226,6 @@
     <t>1 = Less than once a week ; 
 2 = 1 to 5 times a week ; 
 3 = 6 times or more times a week</t>
-  </si>
-  <si>
-    <t>activity_Q01_freq;
-activity_Q02_frequency</t>
   </si>
   <si>
     <t>Cohort: walking-for-leisure 'same as baseline' (CHAMPS items 'activity_Q01_freq'/'activity_Q02_frequency'); these are not in the longitudinal dictionary - ask if there is a newer version of the data dictionary that has these variables.</t>
@@ -2171,9 +2167,6 @@
     <t>Algorithm based on format of the baseline date, but need to confirm.</t>
   </si>
   <si>
-    <t>N_MajorGroup_ISCO08</t>
-  </si>
-  <si>
     <t>Major Group of ISCO-08</t>
   </si>
   <si>
@@ -2258,14 +2251,6 @@
   </si>
   <si>
     <t>Would it be reasonable to consider these variables as walking for leisure (not transport)? Can details about the format/data types for the variable be provided? If integer/numeric, should be able to harmonize based on summing the two variables. Are missing values coded? Confirm if available in follow-up. If so, confirm variable names.</t>
-  </si>
-  <si>
-    <t>activity_Q04_done ; 
-activity_Q09_done ; 
-activity_Q10_done ; 
-activity_Q11_done ; 
-activity_Q12_done ; 
-activity_Q14_done</t>
   </si>
   <si>
     <t>fast cycling past 4 weeks ; 
@@ -2807,6 +2792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2896,7 +2882,7 @@
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>20</v>
@@ -2911,28 +2897,28 @@
         <v>23</v>
       </c>
       <c r="Z1" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="AF1" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:32" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2955,7 +2941,7 @@
         <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>30</v>
@@ -2973,13 +2959,13 @@
         <v>34</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3020,7 +3006,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3061,7 +3047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3102,7 +3088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3158,13 +3144,13 @@
         <v>64</v>
       </c>
       <c r="AA6" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3211,7 +3197,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3264,7 +3250,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3308,7 +3294,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3352,7 +3338,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3402,7 +3388,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3449,7 +3435,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3510,19 +3496,19 @@
         <v>28</v>
       </c>
       <c r="M14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>88</v>
@@ -3540,16 +3526,16 @@
         <v>117</v>
       </c>
       <c r="AA14" s="11" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3599,7 +3585,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="135" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3646,7 +3632,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3693,7 +3679,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3743,7 +3729,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3787,7 +3773,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3837,7 +3823,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3881,7 +3867,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3932,7 +3918,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3961,7 +3947,7 @@
         <v>145</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>173</v>
@@ -3982,10 +3968,10 @@
         <v>174</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -4008,7 +3994,7 @@
         <v>151</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>173</v>
@@ -4029,10 +4015,10 @@
         <v>177</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4076,7 +4062,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4117,7 +4103,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -4167,7 +4153,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -4217,7 +4203,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -4267,7 +4253,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -4317,7 +4303,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -4358,7 +4344,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -4400,7 +4386,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -4444,7 +4430,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -4489,7 +4475,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -4533,7 +4519,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -4577,7 +4563,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -4625,10 +4611,10 @@
         <v>247</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4673,7 +4659,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4718,7 +4704,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4770,7 +4756,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4818,7 +4804,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4870,7 +4856,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4921,7 +4907,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4972,7 +4958,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -5023,16 +5009,16 @@
         <v>102</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>288</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -5077,7 +5063,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -5130,7 +5116,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -5178,10 +5164,10 @@
         <v>304</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -5236,16 +5222,16 @@
         <v>310</v>
       </c>
       <c r="AA49" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AC49" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -5316,25 +5302,25 @@
         <v>317</v>
       </c>
       <c r="N51" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T51" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="O51" s="9" t="s">
+      <c r="U51" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="V51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="W51" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="V51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="W51" s="5" t="s">
-        <v>619</v>
       </c>
       <c r="X51" s="5" t="s">
         <v>88</v>
@@ -5346,7 +5332,7 @@
         <v>318</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
@@ -5375,22 +5361,22 @@
         <v>323</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="O52" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T52" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T52" s="3" t="s">
+      <c r="U52" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="V52" s="5" t="s">
         <v>118</v>
@@ -5408,16 +5394,16 @@
         <v>324</v>
       </c>
       <c r="AA52" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AC52" s="1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -5465,7 +5451,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -5510,7 +5496,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -5555,7 +5541,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="315" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -5600,7 +5586,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -5648,7 +5634,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -5697,7 +5683,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -5746,7 +5732,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="135" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -5817,17 +5803,17 @@
         <v>353</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>354</v>
+        <v>40</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="O61" s="11"/>
       <c r="P61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="V61" s="5" t="s">
         <v>118</v>
@@ -5842,19 +5828,19 @@
         <v>118</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA61" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AC61" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5862,13 +5848,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>50</v>
@@ -5877,7 +5863,7 @@
         <v>352</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>40</v>
@@ -5907,19 +5893,19 @@
         <v>24</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>352</v>
@@ -5928,19 +5914,19 @@
         <v>93</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>635</v>
+        <v>40</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="U63" s="11"/>
       <c r="V63" s="11" t="s">
@@ -5956,19 +5942,19 @@
         <v>118</v>
       </c>
       <c r="Z63" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA63" s="11" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AB63" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AC63" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5976,19 +5962,19 @@
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>93</v>
@@ -6013,7 +5999,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -6021,19 +6007,19 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>352</v>
@@ -6042,10 +6028,10 @@
         <v>93</v>
       </c>
       <c r="M65" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="N65" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="3" t="s">
@@ -6061,10 +6047,10 @@
         <v>102</v>
       </c>
       <c r="Y65" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -6072,29 +6058,29 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="N66" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="N66" s="1" t="s">
+      <c r="O66" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>31</v>
@@ -6109,13 +6095,13 @@
         <v>62</v>
       </c>
       <c r="Y66" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="Z66" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="Z66" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -6123,29 +6109,29 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>50</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="N67" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="O67" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="P67" s="3" t="s">
         <v>31</v>
@@ -6160,13 +6146,13 @@
         <v>62</v>
       </c>
       <c r="Y67" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z67" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="Z67" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -6174,31 +6160,31 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>392</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K68" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="N68" s="3" t="s">
+      <c r="O68" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="P68" s="3" t="s">
         <v>31</v>
@@ -6213,10 +6199,10 @@
         <v>71</v>
       </c>
       <c r="Y68" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" ht="165" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -6224,34 +6210,34 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J69" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="L69" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="M69" s="8" t="s">
+      <c r="N69" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="P69" s="3" t="s">
         <v>31</v>
@@ -6266,13 +6252,13 @@
         <v>102</v>
       </c>
       <c r="Y69" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Z69" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -6280,25 +6266,25 @@
         <v>24</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I70" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="L70" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>40</v>
@@ -6320,16 +6306,16 @@
         <v>118</v>
       </c>
       <c r="Z70" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA70" s="11" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AC70" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -6337,61 +6323,61 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M71" s="8" t="s">
         <v>40</v>
       </c>
       <c r="N71" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="O71" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="O71" s="9" t="s">
+      <c r="P71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z71" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="P71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z71" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="AA71" s="11" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AC71" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -6399,61 +6385,61 @@
         <v>24</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M72" s="8" t="s">
         <v>40</v>
       </c>
       <c r="N72" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="O72" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="O72" s="9" t="s">
+      <c r="P72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z72" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z72" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="AA72" s="11" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AC72" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -6461,61 +6447,61 @@
         <v>24</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M73" s="8" t="s">
         <v>40</v>
       </c>
       <c r="N73" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z73" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="O73" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z73" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="AA73" s="11" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AC73" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6523,25 +6509,25 @@
         <v>24</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>40</v>
@@ -6563,7 +6549,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -6571,25 +6557,25 @@
         <v>24</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>40</v>
@@ -6611,7 +6597,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -6619,28 +6605,28 @@
         <v>24</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="K76" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>40</v>
@@ -6662,16 +6648,16 @@
         <v>118</v>
       </c>
       <c r="Z76" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AA76" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC76" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -6679,61 +6665,61 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M77" s="8" t="s">
         <v>40</v>
       </c>
       <c r="N77" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="O77" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="O77" s="1" t="s">
+      <c r="P77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z77" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="P77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z77" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="AA77" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC77" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -6741,22 +6727,22 @@
         <v>24</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>40</v>
@@ -6778,7 +6764,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -6786,37 +6772,37 @@
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I79" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="K79" s="3" t="s">
+      <c r="L79" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="M79" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="L79" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="N79" s="3" t="s">
+      <c r="O79" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="P79" s="3" t="s">
         <v>31</v>
@@ -6831,10 +6817,10 @@
         <v>71</v>
       </c>
       <c r="Y79" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -6842,28 +6828,28 @@
         <v>24</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="E80" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K80" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="M80" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="P80" s="3" t="s">
         <v>31</v>
@@ -6878,10 +6864,10 @@
         <v>71</v>
       </c>
       <c r="Y80" s="4" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -6889,61 +6875,61 @@
         <v>24</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J81" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K81" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>481</v>
-      </c>
       <c r="L81" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M81" s="8" t="s">
         <v>40</v>
       </c>
       <c r="N81" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="O81" s="9" t="s">
+      <c r="P81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="W81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y81" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z81" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z81" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="AA81" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC81" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -6951,22 +6937,22 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>40</v>
@@ -6988,19 +6974,19 @@
         <v>118</v>
       </c>
       <c r="Z82" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA82" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AB82" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="AC82" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="83" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -7008,22 +6994,22 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>40</v>
@@ -7045,13 +7031,13 @@
         <v>118</v>
       </c>
       <c r="AA83" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC83" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="84" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -7059,22 +7045,22 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>40</v>
@@ -7096,13 +7082,13 @@
         <v>118</v>
       </c>
       <c r="AA84" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC84" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -7110,22 +7096,22 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M85" s="1" t="s">
         <v>40</v>
@@ -7147,13 +7133,13 @@
         <v>118</v>
       </c>
       <c r="AA85" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC85" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -7161,22 +7147,22 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>40</v>
@@ -7198,13 +7184,13 @@
         <v>118</v>
       </c>
       <c r="AA86" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC86" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -7212,22 +7198,22 @@
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>40</v>
@@ -7249,13 +7235,13 @@
         <v>118</v>
       </c>
       <c r="AA87" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC87" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -7263,22 +7249,22 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>40</v>
@@ -7300,13 +7286,13 @@
         <v>118</v>
       </c>
       <c r="AA88" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC88" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -7314,22 +7300,22 @@
         <v>24</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>40</v>
@@ -7351,13 +7337,13 @@
         <v>118</v>
       </c>
       <c r="AA89" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC89" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -7365,22 +7351,22 @@
         <v>24</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>40</v>
@@ -7402,13 +7388,13 @@
         <v>118</v>
       </c>
       <c r="AA90" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC90" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7416,22 +7402,22 @@
         <v>24</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>40</v>
@@ -7453,13 +7439,13 @@
         <v>118</v>
       </c>
       <c r="AA91" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC91" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7467,58 +7453,58 @@
         <v>24</v>
       </c>
       <c r="C92" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>40</v>
       </c>
       <c r="N92" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="O92" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="O92" s="9" t="s">
+      <c r="P92" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="W92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y92" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z92" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="P92" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z92" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="AA92" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC92" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7526,22 +7512,22 @@
         <v>24</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>40</v>
@@ -7563,13 +7549,13 @@
         <v>118</v>
       </c>
       <c r="AA93" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC93" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="94" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -7577,22 +7563,22 @@
         <v>24</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="E94" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>40</v>
@@ -7614,13 +7600,13 @@
         <v>118</v>
       </c>
       <c r="AA94" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC94" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="95" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7628,22 +7614,22 @@
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="E95" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>40</v>
@@ -7665,13 +7651,13 @@
         <v>118</v>
       </c>
       <c r="AA95" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC95" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -7679,22 +7665,22 @@
         <v>24</v>
       </c>
       <c r="C96" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>40</v>
@@ -7716,13 +7702,13 @@
         <v>118</v>
       </c>
       <c r="AA96" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC96" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7730,22 +7716,22 @@
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>40</v>
@@ -7767,13 +7753,13 @@
         <v>118</v>
       </c>
       <c r="AA97" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC97" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -7781,22 +7767,22 @@
         <v>24</v>
       </c>
       <c r="C98" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>40</v>
@@ -7818,13 +7804,13 @@
         <v>118</v>
       </c>
       <c r="AA98" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC98" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7832,22 +7818,22 @@
         <v>24</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M99" s="1" t="s">
         <v>40</v>
@@ -7869,13 +7855,13 @@
         <v>118</v>
       </c>
       <c r="AA99" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC99" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7883,22 +7869,22 @@
         <v>24</v>
       </c>
       <c r="C100" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>40</v>
@@ -7920,13 +7906,13 @@
         <v>118</v>
       </c>
       <c r="AA100" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AC100" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7934,22 +7920,22 @@
         <v>24</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="E101" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>40</v>
@@ -7971,7 +7957,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -7979,41 +7965,41 @@
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M102" s="11" t="s">
         <v>40</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="O102" s="9"/>
       <c r="P102" s="3" t="s">
         <v>31</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="V102" s="5" t="s">
         <v>88</v>
       </c>
       <c r="W102" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="X102" s="5" t="s">
         <v>88</v>
@@ -8022,13 +8008,13 @@
         <v>88</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AB102" s="11" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -8036,22 +8022,22 @@
         <v>24</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>40</v>
@@ -8073,7 +8059,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -8081,31 +8067,31 @@
         <v>24</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>560</v>
-      </c>
       <c r="E104" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J104" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="M104" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="M104" s="1" t="s">
+      <c r="N104" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="N104" s="3" t="s">
+      <c r="O104" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="O104" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="P104" s="3" t="s">
         <v>31</v>
@@ -8123,10 +8109,10 @@
         <v>81</v>
       </c>
       <c r="Z104" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="105" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="105" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -8134,31 +8120,31 @@
         <v>24</v>
       </c>
       <c r="C105" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>567</v>
-      </c>
       <c r="E105" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J105" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="M105" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="L105" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="M105" s="1" t="s">
+      <c r="N105" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="N105" s="3" t="s">
-        <v>570</v>
-      </c>
       <c r="O105" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P105" s="3" t="s">
         <v>31</v>
@@ -8176,10 +8162,10 @@
         <v>81</v>
       </c>
       <c r="Z105" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -8187,31 +8173,31 @@
         <v>24</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>573</v>
-      </c>
       <c r="E106" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M106" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="N106" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="N106" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="O106" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P106" s="3" t="s">
         <v>31</v>
@@ -8229,7 +8215,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -8237,19 +8223,19 @@
         <v>24</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>577</v>
-      </c>
       <c r="E107" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>40</v>
@@ -8271,7 +8257,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -8279,19 +8265,19 @@
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>580</v>
-      </c>
       <c r="E108" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>40</v>
@@ -8313,7 +8299,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8321,19 +8307,19 @@
         <v>24</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>583</v>
-      </c>
       <c r="E109" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>40</v>
@@ -8355,7 +8341,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8363,19 +8349,19 @@
         <v>24</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="E110" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1" t="s">
@@ -8398,7 +8384,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8406,28 +8392,28 @@
         <v>24</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>589</v>
-      </c>
       <c r="E111" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J111" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="M111" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="M111" s="1" t="s">
+      <c r="N111" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="N111" s="1" t="s">
+      <c r="O111" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="P111" s="3" t="s">
         <v>31</v>
@@ -8442,13 +8428,13 @@
         <v>102</v>
       </c>
       <c r="Y111" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="Z111" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="Z111" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8456,19 +8442,19 @@
         <v>24</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>597</v>
-      </c>
       <c r="E112" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L112" s="1"/>
       <c r="M112" s="1" t="s">
@@ -8491,7 +8477,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -8499,19 +8485,19 @@
         <v>24</v>
       </c>
       <c r="C113" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>599</v>
-      </c>
       <c r="E113" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
@@ -8535,7 +8521,54 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AF113" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="activity_Q01_freq;_x000a_activity_Q02_frequency"/>
+        <filter val="activity_Q04_done ; _x000a_activity_Q09_done ; _x000a_activity_Q10_done ; _x000a_activity_Q11_done ; _x000a_activity_Q12_done ; _x000a_activity_Q14_done"/>
+        <filter val="Age.ph2"/>
+        <filter val="bmi.ph2"/>
+        <filter val="Deelnemer_ID"/>
+        <filter val="employ_cat.ph2"/>
+        <filter val="HbA1c_mol.ph2"/>
+        <filter val="HDL.ph2"/>
+        <filter val="Height.ph2"/>
+        <filter val="LDL.ph2"/>
+        <filter val="marital_status.ph2"/>
+        <filter val="med_DM.ph2"/>
+        <filter val="med_HT.ph2"/>
+        <filter val="med_LP.ph2"/>
+        <filter val="N_CVD.ph2"/>
+        <filter val="N_GTS_WHO.ph2"/>
+        <filter val="N_MajorGroup_ISCO08"/>
+        <filter val="nit_alcoholtot.ph2"/>
+        <filter val="nit_kcal.ph2"/>
+        <filter val="ODBP.ph2"/>
+        <filter val="OHR.ph2"/>
+        <filter val="OSBP.ph2"/>
+        <filter val="PHQ9_Q1.ph2 ; PHQ9_Q2.ph2 ;  PHQ9_Q3.ph2 ;  PHQ9_Q4.ph2 ;  PHQ9_Q5.ph2 ;  PHQ9_Q6.ph2 ;  PHQ9_Q7.ph2 ;  PHQ9_Q8.ph2 ;  PHQ9_Q9.ph2"/>
+        <filter val="PSQI_comp1_subjective_sleepquality"/>
+        <filter val="PSQI_comp3_sleep_duratation"/>
+        <filter val="SEX"/>
+        <filter val="SF36_Q01.ph2"/>
+        <filter val="SF36_Q03.ph2 ; SF36_Q04.ph2 ; SF36_Q05.ph2 ; SF36_Q06.ph2 ; SF36_Q07.ph2 ; SF36_Q08.ph2 ; SF36_Q09.ph2 ; SF36_Q10.ph2 ; SF36_Q11.ph2 ; SF36_Q12.ph2"/>
+        <filter val="smoking_4cat.ph2"/>
+        <filter val="Tot_chol.ph2"/>
+        <filter val="Tot_chol.ph2 ; HDL.ph2 ; Triglyc.ph2"/>
+        <filter val="TOTALPA.ph2"/>
+        <filter val="Triglyc.ph2"/>
+        <filter val="Visit1_date.ph2"/>
+        <filter val="waist.ph2"/>
+        <filter val="Weight.ph2"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="21">
+      <filters>
+        <filter val="impossible"/>
+        <filter val="undetermined"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>

--- a/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-MSN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\MSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7595E99-404F-4084-8244-57049F550AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4A43C6-49BF-4D7F-BE49-C77E09659F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="688">
   <si>
     <t>index</t>
   </si>
@@ -391,9 +391,6 @@
   </si>
   <si>
     <t>Cohort: occupation 'same as baseline'. Only 'Occupational_category' is in the longitudinal dictionary; the ISCO/ISEI variables are not - ask if there is a newer version of the data dictionary that has these variables.</t>
-  </si>
-  <si>
-    <t>undetermined</t>
   </si>
   <si>
     <t>sdc_retirement_status</t>
@@ -1095,9 +1092,6 @@
 7 = 9 hours ; 
 8 = 9.5 hours ; 
 9 = 10 hours or more</t>
-  </si>
-  <si>
-    <t>PSQI_comp3_sleep_duratation</t>
   </si>
   <si>
     <t>Cohort: newly added at phase 2 via 'PSQI_comp3_sleep_duratation'; this variable is not in the longitudinal dictionary - ask if there is a newer version of the data dictionary that has this variable. Categorical banding to be defined once the variable's coding is available.</t>
@@ -1485,25 +1479,7 @@
 2 = Presumed no</t>
   </si>
   <si>
-    <t>N_CVD.ph2</t>
-  </si>
-  <si>
-    <t>History of cardiovascular disease;
-Hypertension</t>
-  </si>
-  <si>
-    <t>0 = No history of CVD, 
-1 = History of CVD; 
--999 = missing;
-Hypertension (yes/no) was based on the average blood pressure and antihypertensive medication use. Participants were considered to have hypertension when the average systolic blood pressure ≥ 140 mmHg, or when the diastolic blood pressure ≥90, or when they used antihypertensive medication</t>
-  </si>
-  <si>
     <t>N_HT.ph2 confirmed unavailable by cohort (question sheet, 2026-07-10); hypertension arm removed, CVD-ever now derived from N_CVD.ph2 alone - team to confirm this definition.</t>
-  </si>
-  <si>
-    <t>case_when(N_CVD.ph2 == 1 ~ 1L;
-N_CVD.ph2 == 0 ~ 0L;
-ELSE ~ NA_integer_)</t>
   </si>
   <si>
     <t>dis_cvd_ihd_ever</t>
@@ -1538,9 +1514,6 @@
     <t xml:space="preserve">Acceptable wording is "MI", "Myocardial infarction", or "Heart attack". </t>
   </si>
   <si>
-    <t>Acute myocardial infarction/heart attack ever (from Rose Questionnaire)'</t>
-  </si>
-  <si>
     <t>0 = No, 1 = Yes</t>
   </si>
   <si>
@@ -1561,9 +1534,6 @@
   <si>
     <t xml:space="preserve">Angina pectoris ever (from Rose Questionnaire)
 </t>
-  </si>
-  <si>
-    <t>0 = No, 1 = Yes, 2 = Probably</t>
   </si>
   <si>
     <t>AP_rose.ph2 confirmed unavailable by cohort (question sheet, 2026-07-10); downgraded from complete.</t>
@@ -1745,10 +1715,6 @@
   </si>
   <si>
     <t>If the study did not collect a variable about "ever had any cancer", record the decisions used to derive the DataSchema variable from individual cancers, including whether an "Other cancer" option was available.</t>
-  </si>
-  <si>
-    <t>Do/did you have cancer, other than skin cancer?;
-Do/did you have skin cancer?</t>
   </si>
   <si>
     <t>1 = Yes, 2 = No;
@@ -2167,12 +2133,6 @@
     <t>Algorithm based on format of the baseline date, but need to confirm.</t>
   </si>
   <si>
-    <t>Major Group of ISCO-08</t>
-  </si>
-  <si>
-    <t>0 = Armed Forces Occupations, 1 = Managers, 2 = Professionals, 3 = Technicians and Associate Professionals, 4 = Clerical Support Workers, 5 = Service and Sales Workers, 6 = Skilled Agricultural, Forestry and Fishery Workers, 7 = Craft and Related Trades Workers, 8 = Plant and Machine Operators and Assemblers, 9 = Elementary Occupations</t>
-  </si>
-  <si>
     <t>In baseline: Searched online data dictionary. 
 Currently coded with 'N_MajorGroup_ISCO08' for which category information is available.  Not sure that the level of detail of 'N_Classification_ISCO08' is needed, and we would need to recode every single code to text.
 'N_OccupationalStatusGroup_ISEI08', 'N_Classification_ISEI08' and 'Occupational_category' do not seem as relevant to the DS variable.</t>
@@ -2191,9 +2151,6 @@
     <t>Confirm that smoking_unitsperday.ph2 is not available.</t>
   </si>
   <si>
-    <t>PSQI sleep duration</t>
-  </si>
-  <si>
     <t>0 = GT 7 hours per night; 1 = GT 6 hours and LE 7 hours per night; 2 = GE 5 hours per night and LE 6 hours per night; 3 = LT 5 hours per night;</t>
   </si>
   <si>
@@ -2215,13 +2172,7 @@
     <t>0 = Very good; 1 = Fairly good; 2 = Fairly bad; 3 = Very bad;</t>
   </si>
   <si>
-    <t>PSQI subjective sleep quality</t>
-  </si>
-  <si>
     <t>PSQI component 1 score: subjective sleep quality</t>
-  </si>
-  <si>
-    <t>PSQI_comp1_subjective_sleepquality</t>
   </si>
   <si>
     <t>The study-specific variable categories 0 = Very good and 1 = Fairly good were coded as DataSchema variable category 0 = Never/Rarely. The study-specific variable categories  2 = Fairly bad and 3 = Very bad were coded as DataSchema variable category 1 = Some difficulties.</t>
@@ -2320,19 +2271,7 @@
     <t>smoking_unitsperday.ph2 is available but needs to be requested.</t>
   </si>
   <si>
-    <t>Available, only at FUP, but need to request.
-recode(1=0; 2=0; 3=1; 4=1; ELSE=NA)</t>
-  </si>
-  <si>
     <t>Available, but need to request.</t>
-  </si>
-  <si>
-    <t>Available, but need to request.
-case_when(
-activity_Q04_done == 1 | activity_Q09_done ==1 | activity_Q10_done == 1 | activity_Q11_done ==1 | activity_Q12_done ==1 | activity_Q14_done == 1 ~ 1L ; 
-ELSE ~ NA_integer_)
-Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
-A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
   </si>
   <si>
     <t>Available, need to request.</t>
@@ -2348,6 +2287,182 @@
   </si>
   <si>
     <t>Deelnemer_ID</t>
+  </si>
+  <si>
+    <t>Added/updated.</t>
+  </si>
+  <si>
+    <t>smoking_unitsperday.ph2</t>
+  </si>
+  <si>
+    <t>The study-specific variable label is "Number of cigarettes/cigars/tobacco pipes smoked on an average day".</t>
+  </si>
+  <si>
+    <t>smoking_unitsperday.ph2 * 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available, only at FUP, but need to request.
+</t>
+  </si>
+  <si>
+    <t>activity_Q01_freq.ph2 ; 
+activity_Q02_freq.ph2</t>
+  </si>
+  <si>
+    <t>Study-specific question wording was "In a typical week during the past 4 weeks, how many times a week did you walk...?" Walking for leisure cannot be distinguished from walking for other reasons. The frequency of walking slowly and fast were summed.</t>
+  </si>
+  <si>
+    <t>case_when(
+  (activity_Q01_freq.ph2 + activity_Q02_freq.ph2) &lt; 1 ~ 1L ; 
+  (activity_Q01_freq.ph2 + activity_Q02_freq.ph2) &gt;=1 &amp; (activity_Q01_freq.ph2 + activity_Q02_freq.ph2) &lt;= 5 ~ 2L ;  
+  (activity_Q01_freq.ph2 + activity_Q02_freq.ph2) &gt;=6 ~ 3L ;  
+  ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available, but need to request.
+</t>
+  </si>
+  <si>
+    <t>Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
+A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
+  </si>
+  <si>
+    <t>case_when(
+activity_Q04_done.ph2 == 1 | activity_Q09_done.ph2 ==1 | activity_Q10_done.ph2 == 1 | activity_Q11_done.ph2 ==1 | activity_Q12_done.ph2 ==1 | activity_Q14_done.ph2 == 1 ~ 1L ; 
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>activity_Q04_done.ph2 ; 
+activity_Q09_done.ph2 ; 
+activity_Q10_done.ph2 ; 
+activity_Q11_done.ph2 ; 
+activity_Q12_done.ph2 ; 
+activity_Q14_done.ph2</t>
+  </si>
+  <si>
+    <t>AMI_rose.ph2</t>
+  </si>
+  <si>
+    <t>Acute myocardial infarction/heart attack ever (from Rose Questionnaire)</t>
+  </si>
+  <si>
+    <t>AP_rose.ph2</t>
+  </si>
+  <si>
+    <t>CVA_rose.ph2</t>
+  </si>
+  <si>
+    <t>Positive responses based on acute myocardial infarction/heart attack ever (from Rose Questionnaire) are coded as 1. 0 values in the DataSchema variable cannot be coded.</t>
+  </si>
+  <si>
+    <t>recode(1 = 1 ; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>Study-specific variable is from Rose Questionnaire.</t>
+  </si>
+  <si>
+    <t>recode(0 = 0 ; 1 = 1 ; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>0 = No, 1 = Yes, 2 = Probably (exact pain location and whether the pain disappears within 10 minutes is unknown; other AP criteria are met)</t>
+  </si>
+  <si>
+    <t>Study-specific variable is from Rose Questionnaire. "Probably" is coded as 1.</t>
+  </si>
+  <si>
+    <t>recode(0 = 0 ; 1 = 1 ; 2 = 1 ; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>Hypertension (yes/no) was based on the average blood pressure and antihypertensive medication use. Participants were considered to have hypertension when the average systolic blood pressure ≥ 140 mmHg, or when the diastolic blood pressure ≥90, or when they used antihypertensive medication</t>
+  </si>
+  <si>
+    <t>0 = No history of CVD, 
+1 = History of CVD; 
+-999 = missing;</t>
+  </si>
+  <si>
+    <t>History of cardiovascular disease ; 
+Acute myocardial infarction/heart attack ever (from Rose Questionnaire) ; 
+Angina pectoris ever (from Rose Questionnaire) ; 
+Cerebrovascular accident/stroke ever (from Rose Questionnaire)</t>
+  </si>
+  <si>
+    <t>N_CVD.ph2 ; 
+AMI_rose.ph2 ; 
+AP_rose.ph2 ; 
+CVA_rose.ph2</t>
+  </si>
+  <si>
+    <t>case_when(
+N_CVD.ph2 == 1 | AMI_rose.ph2 == 1 | AP_rose.ph2 == 1 | CVA_rose.ph2 == 1 | N_HT.ph2 == 1 ~ 1L;
+N_CVD.ph2 == 0 ~ 0L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>N_HT.ph2</t>
+  </si>
+  <si>
+    <t>N_HT.ph2 ; 
+med_DM.ph2</t>
+  </si>
+  <si>
+    <t>Hypertension ; 
+Glucose-lowering medication (all types)</t>
+  </si>
+  <si>
+    <t>case_when(
+  N_HT.ph2 == 1 | med_HT.ph2 == 1 ~ 1L ; 
+  N_HT.ph2 == 0 &amp; med_HT.ph2 == 0 ~ 0L ; 
+  N_HT.ph2 == 0 | med_HT.ph2 == 0 ~ 2L ; 
+  ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>Do/did you have skin cancer? ; 
+Do/did you have cancer, other than skin cancer?</t>
+  </si>
+  <si>
+    <t>B1_VD1_2.6.1.ph2 ; 
+B1_VD1_2.6.3.ph2</t>
+  </si>
+  <si>
+    <t>case_when(
+  B1_VD1_2.6.1.ph2 == 1 | B1_VD1_2.6.3.ph2 == 1 ~ 1L  ; 
+  B1_VD1_2.6.1.ph2 == 2 &amp; B1_VD1_2.6.3.ph2 == 2 ~ 0L  ; 
+  ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>The study-specific variable is open text.</t>
+  </si>
+  <si>
+    <t>recode(2 = 0 ; 1 = 1 ; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>Appears to be open text, so considered incompatible.</t>
+  </si>
+  <si>
+    <t>B1_VD1_2.6.4.ph2</t>
+  </si>
+  <si>
+    <t>For which type of cancer (other than skin cancer) have you been monitored by a GP/specialist or admitted to a hospital?</t>
+  </si>
+  <si>
+    <t>B1_VD1_2.6.1.ph2</t>
+  </si>
+  <si>
+    <t>[PSQI_comp3_sleep_duratation] PSQI sleep duration</t>
+  </si>
+  <si>
+    <t>[PSQI_comp1_subjective_sleepquality] PSQI subjective sleep quality</t>
+  </si>
+  <si>
+    <t>This variable was not in the updated dataset, so left as undetermined.
+recode(1=0; 2=0; 3=1; 4=1; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>undetermined</t>
+  </si>
+  <si>
+    <t>There are STED variables in the updated datasets, but there is nothing distinguishing baseline and longitudinal. Can the same STED variables be matched to each data collection event by date of the visit?</t>
   </si>
 </sst>
 </file>
@@ -2411,13 +2526,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2451,16 +2566,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2469,10 +2578,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2792,7 +2907,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2801,14 +2915,14 @@
     <col min="3" max="3" width="28.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="28.5703125" style="3" customWidth="1"/>
     <col min="13" max="13" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="38.85546875" style="1" customWidth="1"/>
     <col min="15" max="15" width="45.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" style="3" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="18" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="46.140625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="27.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="32.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="30.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -2816,8 +2930,9 @@
     <col min="26" max="26" width="50.7109375" style="1" customWidth="1"/>
     <col min="27" max="27" width="61" style="1" customWidth="1"/>
     <col min="28" max="28" width="53" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="43.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="28.7109375" style="3"/>
+    <col min="29" max="29" width="43.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="45.42578125" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="28.7109375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2860,10 +2975,10 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -2881,8 +2996,8 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>619</v>
+      <c r="U1" s="9" t="s">
+        <v>607</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>20</v>
@@ -2896,29 +3011,29 @@
       <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="12" t="s">
-        <v>599</v>
+      <c r="Z1" s="9" t="s">
+        <v>590</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>603</v>
+        <v>592</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2941,9 +3056,9 @@
         <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="N2" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="P2" s="3" t="s">
@@ -2959,13 +3074,13 @@
         <v>34</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3006,7 +3121,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3047,7 +3162,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3088,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3119,7 +3234,7 @@
       <c r="M6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="1" t="s">
         <v>59</v>
       </c>
       <c r="O6" s="1" t="s">
@@ -3143,14 +3258,14 @@
       <c r="Z6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA6" s="11" t="s">
-        <v>606</v>
-      </c>
-      <c r="AC6" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="AA6" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3175,7 +3290,7 @@
       <c r="M7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="1" t="s">
         <v>67</v>
       </c>
       <c r="O7" s="1" t="s">
@@ -3197,7 +3312,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3228,7 +3343,7 @@
       <c r="M8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="1" t="s">
         <v>80</v>
       </c>
       <c r="O8" s="1" t="s">
@@ -3250,7 +3365,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3294,7 +3409,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3338,7 +3453,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3366,7 +3481,7 @@
       <c r="M11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="1" t="s">
         <v>100</v>
       </c>
       <c r="O11" s="1" t="s">
@@ -3388,7 +3503,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3435,7 +3550,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3495,47 +3610,41 @@
       <c r="F14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="W14" s="5" t="s">
+      <c r="U14" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="X14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y14" s="5" t="s">
+      <c r="X14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>88</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AA14" s="11" t="s">
-        <v>611</v>
+      <c r="AA14" s="1" t="s">
+        <v>600</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3543,31 +3652,31 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="1" t="s">
         <v>100</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>31</v>
@@ -3582,10 +3691,10 @@
         <v>102</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="135" hidden="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="135" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3593,28 +3702,28 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="O16" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>31</v>
@@ -3629,10 +3738,10 @@
         <v>102</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3640,25 +3749,25 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>40</v>
@@ -3678,8 +3787,11 @@
       <c r="Y17" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="AD17" s="12" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3687,31 +3799,31 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>31</v>
@@ -3726,10 +3838,10 @@
         <v>102</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3737,25 +3849,25 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>31</v>
@@ -3770,10 +3882,10 @@
         <v>102</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3781,31 +3893,31 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>31</v>
@@ -3820,10 +3932,10 @@
         <v>102</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3831,25 +3943,25 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>31</v>
@@ -3864,10 +3976,10 @@
         <v>102</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3875,32 +3987,32 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>31</v>
@@ -3915,10 +4027,10 @@
         <v>102</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3926,31 +4038,31 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="M23" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>173</v>
+        <v>628</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>31</v>
@@ -3965,13 +4077,13 @@
         <v>102</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3979,25 +4091,25 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>173</v>
+        <v>628</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>31</v>
@@ -4012,33 +4124,33 @@
         <v>102</v>
       </c>
       <c r="Y24" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>40</v>
@@ -4059,10 +4171,10 @@
         <v>88</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4070,13 +4182,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>50</v>
@@ -4100,10 +4212,10 @@
         <v>88</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -4111,31 +4223,31 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>31</v>
@@ -4150,10 +4262,10 @@
         <v>102</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -4161,31 +4273,31 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="M28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>31</v>
@@ -4200,10 +4312,10 @@
         <v>102</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -4211,31 +4323,31 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="M29" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>31</v>
@@ -4250,10 +4362,10 @@
         <v>102</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -4261,25 +4373,25 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="K30" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>40</v>
@@ -4300,10 +4412,10 @@
         <v>88</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -4311,19 +4423,19 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>40</v>
@@ -4344,7 +4456,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -4352,19 +4464,19 @@
         <v>24</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
@@ -4386,7 +4498,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -4394,25 +4506,25 @@
         <v>24</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>31</v>
@@ -4427,10 +4539,10 @@
         <v>102</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -4438,26 +4550,26 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="N34" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>31</v>
@@ -4472,10 +4584,10 @@
         <v>102</v>
       </c>
       <c r="Y34" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -4483,25 +4595,25 @@
         <v>24</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M35" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>31</v>
@@ -4516,10 +4628,10 @@
         <v>102</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -4527,25 +4639,25 @@
         <v>24</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M36" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>31</v>
@@ -4560,10 +4672,10 @@
         <v>102</v>
       </c>
       <c r="Y36" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -4571,29 +4683,29 @@
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>31</v>
@@ -4608,13 +4720,13 @@
         <v>102</v>
       </c>
       <c r="Y37" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4622,26 +4734,26 @@
         <v>24</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>31</v>
@@ -4656,10 +4768,10 @@
         <v>102</v>
       </c>
       <c r="Y38" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4667,19 +4779,19 @@
         <v>24</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
@@ -4701,10 +4813,10 @@
         <v>88</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4712,31 +4824,30 @@
         <v>24</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="9"/>
+      <c r="O40" s="7"/>
       <c r="P40" s="3" t="s">
         <v>31</v>
       </c>
@@ -4753,10 +4864,10 @@
         <v>88</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4764,27 +4875,27 @@
         <v>24</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K41" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O41" s="9"/>
+      <c r="O41" s="7"/>
       <c r="P41" s="3" t="s">
         <v>31</v>
       </c>
@@ -4801,10 +4912,10 @@
         <v>88</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4812,31 +4923,31 @@
         <v>24</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O42" s="9"/>
+      <c r="O42" s="7"/>
       <c r="P42" s="3" t="s">
         <v>31</v>
       </c>
@@ -4853,10 +4964,10 @@
         <v>88</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4864,30 +4975,30 @@
         <v>24</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J43" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="L43" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O43" s="9"/>
+      <c r="O43" s="7"/>
       <c r="P43" s="3" t="s">
         <v>31</v>
       </c>
@@ -4904,10 +5015,10 @@
         <v>88</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4915,29 +5026,29 @@
         <v>24</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="O44" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>31</v>
@@ -4952,13 +5063,13 @@
         <v>102</v>
       </c>
       <c r="Y44" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z44" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="Z44" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4966,35 +5077,35 @@
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G45" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>278</v>
+      <c r="O45" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>31</v>
@@ -5009,16 +5120,16 @@
         <v>102</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -5026,24 +5137,24 @@
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O46" s="9"/>
+      <c r="O46" s="7"/>
       <c r="P46" s="3" t="s">
         <v>31</v>
       </c>
@@ -5060,10 +5171,10 @@
         <v>88</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" ht="135" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -5071,34 +5182,34 @@
         <v>24</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>31</v>
@@ -5113,10 +5224,10 @@
         <v>102</v>
       </c>
       <c r="Y47" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -5124,27 +5235,27 @@
         <v>24</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O48" s="9"/>
+      <c r="O48" s="7"/>
       <c r="P48" s="3" t="s">
         <v>31</v>
       </c>
@@ -5161,13 +5272,13 @@
         <v>88</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -5175,63 +5286,69 @@
         <v>24</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="L49" s="1"/>
-      <c r="M49" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N49" s="3" t="s">
+      <c r="O49" s="7"/>
+      <c r="P49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U49" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="V49" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W49" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X49" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y49" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="Z49" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="O49" s="9"/>
-      <c r="P49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V49" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W49" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X49" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y49" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z49" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AA49" s="11" t="s">
-        <v>612</v>
+      <c r="AA49" s="1" t="s">
+        <v>601</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+      <c r="AC49" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="AD49" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -5239,13 +5356,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>112</v>
@@ -5256,7 +5373,7 @@
       <c r="M50" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O50" s="9"/>
+      <c r="O50" s="7"/>
       <c r="P50" s="3" t="s">
         <v>31</v>
       </c>
@@ -5273,7 +5390,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="135" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="135" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -5281,61 +5398,61 @@
         <v>24</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J51" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="M51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="V51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z51" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="V51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="W51" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="X51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z51" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="AB51" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -5343,67 +5460,70 @@
         <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K52" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="O52" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="V52" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="W52" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="X52" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="Y52" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="Z52" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="V52" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W52" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X52" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y52" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z52" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA52" s="11" t="s">
-        <v>627</v>
+      <c r="AA52" s="1" t="s">
+        <v>613</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="AC52" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>646</v>
+      </c>
+      <c r="AD52" s="12" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -5411,27 +5531,27 @@
         <v>24</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O53" s="9"/>
+      <c r="O53" s="7"/>
       <c r="P53" s="3" t="s">
         <v>31</v>
       </c>
@@ -5448,10 +5568,10 @@
         <v>88</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -5459,24 +5579,24 @@
         <v>24</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O54" s="9"/>
+      <c r="O54" s="7"/>
       <c r="P54" s="3" t="s">
         <v>31</v>
       </c>
@@ -5493,10 +5613,10 @@
         <v>88</v>
       </c>
       <c r="Z54" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -5504,24 +5624,24 @@
         <v>24</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O55" s="9"/>
+      <c r="O55" s="7"/>
       <c r="P55" s="3" t="s">
         <v>31</v>
       </c>
@@ -5538,10 +5658,10 @@
         <v>88</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" ht="315" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="315" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -5549,24 +5669,24 @@
         <v>24</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O56" s="9"/>
+      <c r="O56" s="7"/>
       <c r="P56" s="3" t="s">
         <v>31</v>
       </c>
@@ -5583,10 +5703,10 @@
         <v>88</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -5594,27 +5714,27 @@
         <v>24</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O57" s="9"/>
+      <c r="O57" s="7"/>
       <c r="P57" s="3" t="s">
         <v>31</v>
       </c>
@@ -5631,10 +5751,10 @@
         <v>88</v>
       </c>
       <c r="Z57" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -5642,28 +5762,27 @@
         <v>24</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N58" s="1"/>
-      <c r="O58" s="9"/>
+      <c r="O58" s="7"/>
       <c r="P58" s="3" t="s">
         <v>31</v>
       </c>
@@ -5680,10 +5799,10 @@
         <v>88</v>
       </c>
       <c r="Z58" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -5691,13 +5810,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>112</v>
@@ -5706,13 +5825,13 @@
         <v>113</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O59" s="9"/>
+      <c r="O59" s="7"/>
       <c r="P59" s="3" t="s">
         <v>31</v>
       </c>
@@ -5729,10 +5848,10 @@
         <v>88</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" ht="135" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -5740,24 +5859,24 @@
         <v>24</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O60" s="9"/>
+      <c r="O60" s="7"/>
       <c r="P60" s="3" t="s">
         <v>31</v>
       </c>
@@ -5774,10 +5893,10 @@
         <v>88</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="61" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5785,62 +5904,68 @@
         <v>24</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K61" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="O61" s="7"/>
+      <c r="P61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="U61" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="V61" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W61" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X61" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y61" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="Z61" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="L61" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="M61" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="O61" s="11"/>
-      <c r="P61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T61" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="V61" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W61" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X61" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y61" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z61" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="AA61" s="11" t="s">
-        <v>632</v>
+      <c r="AA61" s="1" t="s">
+        <v>618</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="AC61" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" ht="105" hidden="1" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+      <c r="AC61" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="AD61" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5848,27 +5973,27 @@
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O62" s="9"/>
+      <c r="O62" s="7"/>
       <c r="P62" s="3" t="s">
         <v>31</v>
       </c>
@@ -5885,7 +6010,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="255" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5893,68 +6018,73 @@
         <v>24</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="11" t="s">
-        <v>40</v>
+      <c r="M63" s="10" t="s">
+        <v>653</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="P63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="U63" s="11"/>
-      <c r="V63" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W63" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X63" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y63" s="11" t="s">
-        <v>118</v>
+        <v>620</v>
+      </c>
+      <c r="U63" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="V63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W63" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X63" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y63" s="10" t="s">
+        <v>652</v>
       </c>
       <c r="Z63" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="AA63" s="11" t="s">
-        <v>635</v>
+        <v>361</v>
+      </c>
+      <c r="AA63" s="1" t="s">
+        <v>621</v>
       </c>
       <c r="AB63" s="1" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="AC63" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+      <c r="AD63" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5962,19 +6092,19 @@
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>93</v>
@@ -5982,7 +6112,7 @@
       <c r="M64" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O64" s="9"/>
+      <c r="O64" s="7"/>
       <c r="P64" s="3" t="s">
         <v>31</v>
       </c>
@@ -5999,7 +6129,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -6007,33 +6137,33 @@
         <v>24</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="O65" s="9"/>
+        <v>370</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="O65" s="7"/>
       <c r="P65" s="3" t="s">
         <v>31</v>
       </c>
@@ -6047,10 +6177,10 @@
         <v>102</v>
       </c>
       <c r="Y65" s="4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -6058,29 +6188,29 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>31</v>
@@ -6095,13 +6225,13 @@
         <v>62</v>
       </c>
       <c r="Y66" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Z66" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -6109,29 +6239,29 @@
         <v>24</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>50</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="O67" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="P67" s="3" t="s">
         <v>31</v>
@@ -6146,13 +6276,13 @@
         <v>62</v>
       </c>
       <c r="Y67" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Z67" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -6160,31 +6290,31 @@
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K68" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M68" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="O68" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="P68" s="3" t="s">
         <v>31</v>
@@ -6199,10 +6329,10 @@
         <v>71</v>
       </c>
       <c r="Y68" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" ht="165" hidden="1" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" ht="105" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -6210,37 +6340,40 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J69" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="K69" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M69" s="8" t="s">
-        <v>404</v>
+      <c r="M69" s="10" t="s">
+        <v>668</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>405</v>
+        <v>667</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>406</v>
+        <v>666</v>
       </c>
       <c r="P69" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>32</v>
@@ -6251,14 +6384,14 @@
       <c r="X69" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y69" s="4" t="s">
-        <v>408</v>
+      <c r="Y69" s="10" t="s">
+        <v>669</v>
       </c>
       <c r="Z69" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -6266,56 +6399,62 @@
         <v>24</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O70" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="O70" s="7"/>
       <c r="P70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V70" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W70" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X70" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y70" s="5" t="s">
-        <v>118</v>
+      <c r="U70" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="V70" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W70" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X70" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y70" s="10" t="s">
+        <v>659</v>
       </c>
       <c r="Z70" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="AA70" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="AC70" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="AA70" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC70" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD70" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -6323,61 +6462,67 @@
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="J71" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="O71" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M71" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="P71" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y71" s="5" t="s">
-        <v>118</v>
+      <c r="U71" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="V71" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W71" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X71" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y71" s="10" t="s">
+        <v>661</v>
       </c>
       <c r="Z71" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="AA71" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="AC71" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="AA71" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC71" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD71" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -6385,61 +6530,67 @@
         <v>24</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M72" s="8" t="s">
-        <v>40</v>
+        <v>401</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>427</v>
+        <v>419</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>662</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y72" s="5" t="s">
-        <v>118</v>
+      <c r="U72" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="V72" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W72" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X72" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y72" s="10" t="s">
+        <v>664</v>
       </c>
       <c r="Z72" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="AA72" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="AA72" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC72" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD72" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -6447,61 +6598,67 @@
         <v>24</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="J73" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="O73" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M73" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="P73" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X73" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y73" s="5" t="s">
-        <v>118</v>
+      <c r="U73" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="V73" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W73" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X73" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y73" s="10" t="s">
+        <v>661</v>
       </c>
       <c r="Z73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="AA73" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="AC73" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="AA73" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC73" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD73" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6509,30 +6666,30 @@
         <v>24</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O74" s="9"/>
+      <c r="O74" s="7"/>
       <c r="P74" s="3" t="s">
         <v>31</v>
       </c>
@@ -6549,7 +6706,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -6557,30 +6714,30 @@
         <v>24</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O75" s="9"/>
+      <c r="O75" s="7"/>
       <c r="P75" s="3" t="s">
         <v>31</v>
       </c>
@@ -6597,7 +6754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -6605,59 +6762,67 @@
         <v>24</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="N76" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="O76" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O76" s="9"/>
       <c r="P76" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V76" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W76" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X76" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y76" s="5" t="s">
-        <v>118</v>
+      <c r="V76" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W76" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X76" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y76" s="10" t="s">
+        <v>661</v>
       </c>
       <c r="Z76" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="AA76" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+      <c r="AA76" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC76" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD76" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -6665,61 +6830,64 @@
         <v>24</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M77" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>454</v>
+        <v>401</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>672</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="P77" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="X77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y77" s="5" t="s">
-        <v>118</v>
+      <c r="V77" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W77" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X77" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y77" s="10" t="s">
+        <v>673</v>
       </c>
       <c r="Z77" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AA77" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="AC77" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="AA77" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC77" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD77" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -6727,27 +6895,27 @@
         <v>24</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O78" s="9"/>
+      <c r="O78" s="7"/>
       <c r="P78" s="3" t="s">
         <v>31</v>
       </c>
@@ -6764,7 +6932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -6772,37 +6940,37 @@
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="J79" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="P79" s="3" t="s">
         <v>31</v>
@@ -6817,10 +6985,10 @@
         <v>71</v>
       </c>
       <c r="Y79" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -6828,28 +6996,28 @@
         <v>24</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="M80" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="P80" s="3" t="s">
         <v>31</v>
@@ -6864,10 +7032,10 @@
         <v>71</v>
       </c>
       <c r="Y80" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -6875,61 +7043,64 @@
         <v>24</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M81" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>482</v>
+        <v>401</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X81" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y81" s="11" t="s">
-        <v>118</v>
+      <c r="V81" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W81" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X81" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y81" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="Z81" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA81" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+      <c r="AA81" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC81" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD81" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -6937,56 +7108,67 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O82" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M82" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N82" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O82" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P82" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V82" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W82" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X82" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y82" s="11" t="s">
-        <v>118</v>
+      <c r="U82" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V82" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W82" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X82" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y82" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="Z82" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="AA82" s="11" t="s">
-        <v>637</v>
+        <v>479</v>
+      </c>
+      <c r="AA82" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AB82" s="1" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="AC82" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="83" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="AD82" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -6994,50 +7176,61 @@
         <v>24</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O83" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P83" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V83" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W83" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X83" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y83" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA83" s="11" t="s">
-        <v>637</v>
+      <c r="U83" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V83" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W83" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X83" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y83" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA83" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC83" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="84" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD83" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -7045,50 +7238,61 @@
         <v>24</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O84" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O84" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P84" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V84" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W84" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X84" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y84" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA84" s="11" t="s">
-        <v>637</v>
+      <c r="U84" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V84" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W84" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X84" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y84" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA84" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC84" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD84" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -7096,50 +7300,61 @@
         <v>24</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O85" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O85" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P85" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V85" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W85" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X85" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y85" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA85" s="11" t="s">
-        <v>637</v>
+      <c r="U85" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V85" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W85" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X85" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y85" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA85" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC85" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD85" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -7147,50 +7362,61 @@
         <v>24</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O86" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M86" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N86" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O86" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P86" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V86" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W86" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X86" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y86" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA86" s="11" t="s">
-        <v>637</v>
+      <c r="U86" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V86" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W86" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X86" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y86" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA86" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC86" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD86" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -7198,50 +7424,61 @@
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O87" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O87" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P87" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V87" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W87" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X87" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y87" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA87" s="11" t="s">
-        <v>637</v>
+      <c r="U87" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V87" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W87" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X87" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y87" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA87" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC87" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD87" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -7249,50 +7486,61 @@
         <v>24</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O88" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M88" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N88" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O88" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P88" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V88" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W88" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X88" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y88" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA88" s="11" t="s">
-        <v>637</v>
+      <c r="U88" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V88" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W88" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X88" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y88" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA88" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC88" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD88" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -7300,50 +7548,61 @@
         <v>24</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O89" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O89" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P89" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V89" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W89" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X89" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y89" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA89" s="11" t="s">
-        <v>637</v>
+      <c r="U89" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V89" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W89" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X89" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y89" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA89" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC89" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD89" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -7351,50 +7610,61 @@
         <v>24</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O90" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O90" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P90" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V90" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W90" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X90" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y90" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA90" s="11" t="s">
-        <v>637</v>
+      <c r="U90" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V90" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W90" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X90" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y90" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA90" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC90" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD90" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7402,50 +7672,61 @@
         <v>24</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O91" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O91" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P91" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V91" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W91" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X91" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y91" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA91" s="11" t="s">
-        <v>637</v>
+      <c r="U91" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V91" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W91" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X91" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y91" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA91" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC91" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD91" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7453,58 +7734,61 @@
         <v>24</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>40</v>
+        <v>401</v>
+      </c>
+      <c r="M92" s="10" t="s">
+        <v>682</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="O92" s="9" t="s">
-        <v>520</v>
+        <v>510</v>
+      </c>
+      <c r="O92" s="7" t="s">
+        <v>511</v>
       </c>
       <c r="P92" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X92" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y92" s="11" t="s">
-        <v>118</v>
+      <c r="V92" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X92" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y92" s="10" t="s">
+        <v>678</v>
       </c>
       <c r="Z92" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="AA92" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="AC92" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="AA92" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC92" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD92" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7512,50 +7796,61 @@
         <v>24</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O93" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O93" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P93" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V93" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W93" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X93" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y93" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA93" s="11" t="s">
-        <v>637</v>
+      <c r="U93" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V93" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W93" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X93" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y93" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA93" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC93" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="94" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD93" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -7563,50 +7858,61 @@
         <v>24</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O94" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N94" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O94" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P94" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V94" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W94" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X94" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y94" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA94" s="11" t="s">
-        <v>637</v>
+      <c r="U94" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V94" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W94" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X94" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y94" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA94" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC94" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="95" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD94" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7614,50 +7920,61 @@
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O95" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O95" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P95" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V95" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W95" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X95" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y95" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA95" s="11" t="s">
-        <v>637</v>
+      <c r="U95" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V95" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W95" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X95" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y95" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA95" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC95" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD95" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -7665,50 +7982,61 @@
         <v>24</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O96" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M96" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N96" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P96" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V96" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W96" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X96" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y96" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA96" s="11" t="s">
-        <v>637</v>
+      <c r="U96" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V96" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W96" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X96" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y96" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA96" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC96" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD96" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7716,50 +8044,61 @@
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O97" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M97" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N97" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P97" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V97" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W97" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X97" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y97" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA97" s="11" t="s">
-        <v>637</v>
+      <c r="U97" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V97" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W97" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X97" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y97" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA97" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC97" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD97" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -7767,50 +8106,61 @@
         <v>24</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O98" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M98" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N98" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O98" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P98" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V98" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W98" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X98" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y98" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA98" s="11" t="s">
-        <v>637</v>
+      <c r="U98" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V98" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W98" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X98" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y98" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA98" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC98" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD98" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7818,50 +8168,61 @@
         <v>24</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O99" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M99" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N99" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O99" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P99" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V99" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W99" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X99" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y99" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA99" s="11" t="s">
-        <v>637</v>
+      <c r="U99" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V99" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W99" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X99" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y99" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA99" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC99" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD99" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7869,50 +8230,61 @@
         <v>24</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O100" s="9"/>
+        <v>401</v>
+      </c>
+      <c r="M100" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="N100" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="O100" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="P100" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V100" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W100" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="X100" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y100" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA100" s="11" t="s">
-        <v>637</v>
+      <c r="U100" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="V100" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W100" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="X100" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y100" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA100" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="AC100" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="AD100" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7920,27 +8292,27 @@
         <v>24</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O101" s="9"/>
+      <c r="O101" s="7"/>
       <c r="P101" s="3" t="s">
         <v>31</v>
       </c>
@@ -7957,7 +8329,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -7965,56 +8337,56 @@
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="M102" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="M102" s="1" t="s">
         <v>40</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="O102" s="9"/>
+        <v>626</v>
+      </c>
+      <c r="O102" s="7"/>
       <c r="P102" s="3" t="s">
         <v>31</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="V102" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="W102" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="X102" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y102" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>88</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="AB102" s="11" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+      <c r="AB102" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -8022,27 +8394,27 @@
         <v>24</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O103" s="9"/>
+      <c r="O103" s="7"/>
       <c r="P103" s="3" t="s">
         <v>31</v>
       </c>
@@ -8059,7 +8431,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -8067,31 +8439,31 @@
         <v>24</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>562</v>
+        <v>552</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="P104" s="3" t="s">
         <v>31</v>
@@ -8109,10 +8481,10 @@
         <v>81</v>
       </c>
       <c r="Z104" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="105" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -8120,31 +8492,31 @@
         <v>24</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="P105" s="3" t="s">
         <v>31</v>
@@ -8162,10 +8534,10 @@
         <v>81</v>
       </c>
       <c r="Z105" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -8173,31 +8545,31 @@
         <v>24</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="P106" s="3" t="s">
         <v>31</v>
@@ -8215,7 +8587,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -8223,24 +8595,24 @@
         <v>24</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O107" s="9"/>
+      <c r="O107" s="7"/>
       <c r="P107" s="3" t="s">
         <v>31</v>
       </c>
@@ -8257,7 +8629,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -8265,24 +8637,24 @@
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O108" s="9"/>
+      <c r="O108" s="7"/>
       <c r="P108" s="3" t="s">
         <v>31</v>
       </c>
@@ -8299,7 +8671,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8307,24 +8679,24 @@
         <v>24</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O109" s="9"/>
+      <c r="O109" s="7"/>
       <c r="P109" s="3" t="s">
         <v>31</v>
       </c>
@@ -8341,7 +8713,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8349,25 +8721,25 @@
         <v>24</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O110" s="9"/>
+      <c r="O110" s="7"/>
       <c r="P110" s="3" t="s">
         <v>31</v>
       </c>
@@ -8384,7 +8756,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8392,28 +8764,28 @@
         <v>24</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="P111" s="3" t="s">
         <v>31</v>
@@ -8427,14 +8799,14 @@
       <c r="X111" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y111" s="10" t="s">
-        <v>593</v>
+      <c r="Y111" s="8" t="s">
+        <v>584</v>
       </c>
       <c r="Z111" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8442,25 +8814,25 @@
         <v>24</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="L112" s="1"/>
       <c r="M112" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O112" s="9"/>
+      <c r="O112" s="7"/>
       <c r="P112" s="3" t="s">
         <v>31</v>
       </c>
@@ -8477,7 +8849,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -8485,25 +8857,25 @@
         <v>24</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>50</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O113" s="9"/>
+      <c r="O113" s="7"/>
       <c r="P113" s="3" t="s">
         <v>31</v>
       </c>
@@ -8521,54 +8893,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF113" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="activity_Q01_freq;_x000a_activity_Q02_frequency"/>
-        <filter val="activity_Q04_done ; _x000a_activity_Q09_done ; _x000a_activity_Q10_done ; _x000a_activity_Q11_done ; _x000a_activity_Q12_done ; _x000a_activity_Q14_done"/>
-        <filter val="Age.ph2"/>
-        <filter val="bmi.ph2"/>
-        <filter val="Deelnemer_ID"/>
-        <filter val="employ_cat.ph2"/>
-        <filter val="HbA1c_mol.ph2"/>
-        <filter val="HDL.ph2"/>
-        <filter val="Height.ph2"/>
-        <filter val="LDL.ph2"/>
-        <filter val="marital_status.ph2"/>
-        <filter val="med_DM.ph2"/>
-        <filter val="med_HT.ph2"/>
-        <filter val="med_LP.ph2"/>
-        <filter val="N_CVD.ph2"/>
-        <filter val="N_GTS_WHO.ph2"/>
-        <filter val="N_MajorGroup_ISCO08"/>
-        <filter val="nit_alcoholtot.ph2"/>
-        <filter val="nit_kcal.ph2"/>
-        <filter val="ODBP.ph2"/>
-        <filter val="OHR.ph2"/>
-        <filter val="OSBP.ph2"/>
-        <filter val="PHQ9_Q1.ph2 ; PHQ9_Q2.ph2 ;  PHQ9_Q3.ph2 ;  PHQ9_Q4.ph2 ;  PHQ9_Q5.ph2 ;  PHQ9_Q6.ph2 ;  PHQ9_Q7.ph2 ;  PHQ9_Q8.ph2 ;  PHQ9_Q9.ph2"/>
-        <filter val="PSQI_comp1_subjective_sleepquality"/>
-        <filter val="PSQI_comp3_sleep_duratation"/>
-        <filter val="SEX"/>
-        <filter val="SF36_Q01.ph2"/>
-        <filter val="SF36_Q03.ph2 ; SF36_Q04.ph2 ; SF36_Q05.ph2 ; SF36_Q06.ph2 ; SF36_Q07.ph2 ; SF36_Q08.ph2 ; SF36_Q09.ph2 ; SF36_Q10.ph2 ; SF36_Q11.ph2 ; SF36_Q12.ph2"/>
-        <filter val="smoking_4cat.ph2"/>
-        <filter val="Tot_chol.ph2"/>
-        <filter val="Tot_chol.ph2 ; HDL.ph2 ; Triglyc.ph2"/>
-        <filter val="TOTALPA.ph2"/>
-        <filter val="Triglyc.ph2"/>
-        <filter val="Visit1_date.ph2"/>
-        <filter val="waist.ph2"/>
-        <filter val="Weight.ph2"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="21">
-      <filters>
-        <filter val="impossible"/>
-        <filter val="undetermined"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
